--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6948,0.1953,0.1024,0.0563</t>
-  </si>
-  <si>
-    <t>0.0142,0.0011,0.0008,0.9940</t>
-  </si>
-  <si>
-    <t>0.4255,0.1298,0.0146,0.6424</t>
-  </si>
-  <si>
-    <t>0.2605,0.0156,0.0099,0.8523</t>
-  </si>
-  <si>
-    <t>0.9943,0.0041,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9931,0.0022,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9880,0.0141,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9914,0.0029,0.0003,0.0016</t>
-  </si>
-  <si>
-    <t>0.9884,0.0060,0.0005,0.0016</t>
-  </si>
-  <si>
-    <t>0.9928,0.0022,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.9959,0.0004,0.0000,0.0012</t>
-  </si>
-  <si>
-    <t>0.9964,0.0013,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.7213,0.0506,0.2441,0.0145</t>
-  </si>
-  <si>
-    <t>0.1066,0.0208,0.8917,0.0015</t>
-  </si>
-  <si>
-    <t>0.6572,0.0152,0.4042,0.0019</t>
-  </si>
-  <si>
-    <t>0.1257,0.0100,0.8975,0.0021</t>
-  </si>
-  <si>
-    <t>0.5487,0.0487,0.4477,0.0466</t>
-  </si>
-  <si>
-    <t>0.0447,0.9590,0.0118,0.0002</t>
-  </si>
-  <si>
-    <t>0.0112,0.9887,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.6285,0.4821,0.0163,0.0026</t>
-  </si>
-  <si>
-    <t>0.0549,0.9560,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.0158,0.9799,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.2123,0.0436,0.7637,0.0056</t>
-  </si>
-  <si>
-    <t>0.5599,0.0095,0.4446,0.0237</t>
-  </si>
-  <si>
-    <t>0.0189,0.0009,0.9872,0.0012</t>
-  </si>
-  <si>
-    <t>0.1982,0.0320,0.7331,0.1030</t>
-  </si>
-  <si>
-    <t>0.0253,0.0037,0.9818,0.0005</t>
-  </si>
-  <si>
-    <t>0.1317,0.0022,0.9039,0.0093</t>
-  </si>
-  <si>
-    <t>0.0244,0.0019,0.9776,0.0033</t>
-  </si>
-  <si>
-    <t>0.7341,0.3434,0.0188,0.0037</t>
-  </si>
-  <si>
-    <t>0.5148,0.3648,0.2172,0.0126</t>
-  </si>
-  <si>
-    <t>0.0001,0.0041,0.9984,0.0019</t>
-  </si>
-  <si>
-    <t>0.0209,0.9383,0.0986,0.0048</t>
-  </si>
-  <si>
-    <t>0.8406,0.1016,0.0651,0.0158</t>
-  </si>
-  <si>
-    <t>0.3225,0.0338,0.7154,0.0067</t>
-  </si>
-  <si>
-    <t>0.8213,0.2538,0.0109,0.0007</t>
-  </si>
-  <si>
-    <t>0.0556,0.8829,0.1995,0.0006</t>
-  </si>
-  <si>
-    <t>0.0288,0.7699,0.3059,0.0564</t>
-  </si>
-  <si>
-    <t>0.1096,0.1904,0.7990,0.0510</t>
-  </si>
-  <si>
-    <t>0.0448,0.1452,0.8921,0.0083</t>
-  </si>
-  <si>
-    <t>0.0851,0.0161,0.3658,0.5847</t>
-  </si>
-  <si>
-    <t>0.0384,0.1989,0.8722,0.0111</t>
-  </si>
-  <si>
-    <t>0.0052,0.9584,0.1436,0.0116</t>
-  </si>
-  <si>
-    <t>0.0731,0.0367,0.9170,0.0055</t>
-  </si>
-  <si>
-    <t>0.1148,0.4459,0.0167,0.8306</t>
-  </si>
-  <si>
-    <t>0.0028,0.9732,0.0386,0.0701</t>
-  </si>
-  <si>
-    <t>0.0065,0.9728,0.1313,0.0011</t>
-  </si>
-  <si>
-    <t>0.0090,0.9734,0.1225,0.0024</t>
-  </si>
-  <si>
-    <t>0.0181,0.0892,0.9558,0.0021</t>
-  </si>
-  <si>
-    <t>0.0003,0.2207,0.9938,0.0001</t>
-  </si>
-  <si>
-    <t>0.0621,0.0276,0.9268,0.0075</t>
-  </si>
-  <si>
-    <t>0.0231,0.0043,0.9727,0.0051</t>
-  </si>
-  <si>
-    <t>0.0016,0.0162,0.9907,0.0020</t>
-  </si>
-  <si>
-    <t>0.0035,0.0136,0.9928,0.0009</t>
-  </si>
-  <si>
-    <t>0.8195,0.2931,0.0067,0.0007</t>
-  </si>
-  <si>
-    <t>0.8604,0.1046,0.0476,0.0024</t>
-  </si>
-  <si>
-    <t>0.9739,0.0172,0.0072,0.0036</t>
-  </si>
-  <si>
-    <t>0.0012,0.2140,0.9881,0.0011</t>
-  </si>
-  <si>
-    <t>0.9614,0.0242,0.0069,0.0096</t>
-  </si>
-  <si>
-    <t>0.9728,0.0109,0.0014,0.0068</t>
-  </si>
-  <si>
-    <t>0.9374,0.0995,0.0058,0.0003</t>
-  </si>
-  <si>
-    <t>0.0018,0.9187,0.7729,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.0849,0.9879,0.0013</t>
-  </si>
-  <si>
-    <t>0.0041,0.0249,0.9636,0.0368</t>
-  </si>
-  <si>
-    <t>0.0002,0.9194,0.9668,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0026,0.9972,0.0013</t>
-  </si>
-  <si>
-    <t>0.0486,0.5973,0.4588,0.0007</t>
-  </si>
-  <si>
-    <t>0.0181,0.9791,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.7311,0.2003,0.1253,0.0361</t>
-  </si>
-  <si>
-    <t>0.7089,0.1954,0.1320,0.0139</t>
-  </si>
-  <si>
-    <t>0.0035,0.0517,0.9878,0.0019</t>
-  </si>
-  <si>
-    <t>0.0006,0.9526,0.8501,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.8559,0.7425,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.9670,0.7272,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.9847,0.5214,0.0002</t>
-  </si>
-  <si>
-    <t>0.0149,0.0016,0.0488,0.9578</t>
-  </si>
-  <si>
-    <t>0.0199,0.0274,0.0017,0.9888</t>
-  </si>
-  <si>
-    <t>0.0085,0.0076,0.0018,0.9943</t>
-  </si>
-  <si>
-    <t>0.0057,0.0064,0.0020,0.9961</t>
-  </si>
-  <si>
-    <t>0.0049,0.0286,0.0020,0.9953</t>
-  </si>
-  <si>
-    <t>0.0100,0.0021,0.0267,0.9729</t>
-  </si>
-  <si>
-    <t>0.0005,0.9534,0.7875,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.5927,0.9754,0.0008</t>
-  </si>
-  <si>
-    <t>0.0177,0.8250,0.3999,0.0019</t>
-  </si>
-  <si>
-    <t>0.0031,0.2111,0.9734,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.9714,0.6846,0.0000</t>
-  </si>
-  <si>
-    <t>0.0097,0.7728,0.7685,0.0046</t>
-  </si>
-  <si>
-    <t>0.9943,0.0027,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9765,0.0108,0.0006,0.0057</t>
-  </si>
-  <si>
-    <t>0.9768,0.0286,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.9924,0.0056,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9764,0.0319,0.0034,0.0003</t>
-  </si>
-  <si>
-    <t>0.9891,0.0109,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9907,0.0043,0.0013,0.0014</t>
-  </si>
-  <si>
-    <t>0.9653,0.0608,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.9918,0.0009,0.0002,0.0045</t>
-  </si>
-  <si>
-    <t>0.9882,0.0110,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9979,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9964,0.0013,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9947,0.0031,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9919,0.0053,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9964,0.0028,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9936,0.0050,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0016,0.9889,0.0196</t>
-  </si>
-  <si>
-    <t>0.1899,0.0098,0.8795,0.0009</t>
-  </si>
-  <si>
-    <t>0.5312,0.0122,0.4342,0.0522</t>
-  </si>
-  <si>
-    <t>0.3847,0.0023,0.7969,0.0011</t>
-  </si>
-  <si>
-    <t>0.0142,0.9810,0.0048,0.0002</t>
-  </si>
-  <si>
-    <t>0.0671,0.9351,0.0135,0.0003</t>
-  </si>
-  <si>
-    <t>0.0680,0.9257,0.0034,0.0026</t>
-  </si>
-  <si>
-    <t>0.3198,0.7449,0.0097,0.0040</t>
-  </si>
-  <si>
-    <t>0.2883,0.7934,0.0092,0.0016</t>
-  </si>
-  <si>
-    <t>0.0617,0.9442,0.0050,0.0010</t>
-  </si>
-  <si>
-    <t>0.8714,0.1642,0.0102,0.0006</t>
-  </si>
-  <si>
-    <t>0.5924,0.0538,0.4238,0.0057</t>
-  </si>
-  <si>
-    <t>0.2093,0.0112,0.8349,0.0033</t>
-  </si>
-  <si>
-    <t>0.6572,0.0445,0.3056,0.0307</t>
-  </si>
-  <si>
-    <t>0.3823,0.0141,0.6914,0.0040</t>
-  </si>
-  <si>
-    <t>0.0861,0.0291,0.0323,0.9329</t>
-  </si>
-  <si>
-    <t>0.0042,0.9852,0.0412,0.0008</t>
-  </si>
-  <si>
-    <t>0.0044,0.9724,0.0616,0.0139</t>
-  </si>
-  <si>
-    <t>0.0308,0.9521,0.0072,0.0108</t>
-  </si>
-  <si>
-    <t>0.0005,0.9396,0.9325,0.0004</t>
-  </si>
-  <si>
-    <t>0.0450,0.9460,0.0540,0.0003</t>
-  </si>
-  <si>
-    <t>0.5434,0.4382,0.0544,0.0009</t>
-  </si>
-  <si>
-    <t>0.5974,0.5042,0.0249,0.0020</t>
-  </si>
-  <si>
-    <t>0.9433,0.0525,0.0134,0.0031</t>
-  </si>
-  <si>
-    <t>0.9749,0.0089,0.0018,0.0102</t>
-  </si>
-  <si>
-    <t>0.9573,0.0118,0.0015,0.0183</t>
-  </si>
-  <si>
-    <t>0.9637,0.0284,0.0042,0.0041</t>
-  </si>
-  <si>
-    <t>0.9878,0.0042,0.0017,0.0027</t>
-  </si>
-  <si>
-    <t>0.9345,0.0465,0.0365,0.0035</t>
-  </si>
-  <si>
-    <t>0.9595,0.0314,0.0119,0.0050</t>
-  </si>
-  <si>
-    <t>0.9741,0.0158,0.0029,0.0035</t>
-  </si>
-  <si>
-    <t>0.0175,0.2954,0.9169,0.0015</t>
-  </si>
-  <si>
-    <t>0.0042,0.2999,0.9588,0.0002</t>
-  </si>
-  <si>
-    <t>0.0068,0.8757,0.5703,0.0010</t>
-  </si>
-  <si>
-    <t>0.0147,0.4473,0.8906,0.0036</t>
-  </si>
-  <si>
-    <t>0.3723,0.0915,0.5898,0.1027</t>
-  </si>
-  <si>
-    <t>0.7590,0.0277,0.1618,0.0391</t>
-  </si>
-  <si>
-    <t>0.4652,0.0072,0.6942,0.0014</t>
-  </si>
-  <si>
-    <t>0.5833,0.2289,0.2713,0.0205</t>
-  </si>
-  <si>
-    <t>0.0651,0.0006,0.0010,0.9744</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.0005,0.9995</t>
-  </si>
-  <si>
-    <t>0.0049,0.0017,0.0026,0.9934</t>
-  </si>
-  <si>
-    <t>0.0237,0.0019,0.0056,0.9830</t>
-  </si>
-  <si>
-    <t>0.0008,0.8260,0.9326,0.0002</t>
-  </si>
-  <si>
-    <t>0.9640,0.0281,0.0061,0.0054</t>
-  </si>
-  <si>
-    <t>0.4040,0.6262,0.0071,0.0147</t>
-  </si>
-  <si>
-    <t>0.9699,0.0107,0.0087,0.0062</t>
-  </si>
-  <si>
-    <t>0.5733,0.5474,0.0129,0.0006</t>
-  </si>
-  <si>
-    <t>0.9525,0.0092,0.0340,0.0048</t>
-  </si>
-  <si>
-    <t>0.0539,0.0144,0.0118,0.9657</t>
-  </si>
-  <si>
-    <t>0.9724,0.0047,0.0023,0.0138</t>
-  </si>
-  <si>
-    <t>0.0042,0.0983,0.9585,0.0298</t>
-  </si>
-  <si>
-    <t>0.8506,0.0084,0.0267,0.1032</t>
-  </si>
-  <si>
-    <t>0.8320,0.0481,0.0061,0.1025</t>
-  </si>
-  <si>
-    <t>0.2872,0.6859,0.0198,0.0555</t>
-  </si>
-  <si>
-    <t>0.9088,0.0368,0.0452,0.0021</t>
-  </si>
-  <si>
-    <t>0.8710,0.1039,0.0338,0.0052</t>
-  </si>
-  <si>
-    <t>0.2818,0.6710,0.0846,0.0267</t>
-  </si>
-  <si>
-    <t>0.5907,0.3708,0.0902,0.0033</t>
-  </si>
-  <si>
-    <t>0.7339,0.2213,0.0823,0.0167</t>
-  </si>
-  <si>
-    <t>0.9863,0.0043,0.0005,0.0039</t>
-  </si>
-  <si>
-    <t>0.9901,0.0054,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.9827,0.0066,0.0026,0.0041</t>
-  </si>
-  <si>
-    <t>0.9781,0.0019,0.0004,0.0138</t>
-  </si>
-  <si>
-    <t>0.9773,0.0104,0.0035,0.0057</t>
-  </si>
-  <si>
-    <t>0.9711,0.0184,0.0071,0.0019</t>
-  </si>
-  <si>
-    <t>0.9824,0.0034,0.0007,0.0061</t>
-  </si>
-  <si>
-    <t>0.9928,0.0029,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.4781,0.6729,0.0062,0.0015</t>
-  </si>
-  <si>
-    <t>0.2784,0.8001,0.0073,0.0006</t>
-  </si>
-  <si>
-    <t>0.5331,0.6329,0.0093,0.0004</t>
-  </si>
-  <si>
-    <t>0.5011,0.3877,0.2460,0.0233</t>
-  </si>
-  <si>
-    <t>0.9785,0.0199,0.0010,0.0019</t>
-  </si>
-  <si>
-    <t>0.9095,0.0725,0.0095,0.0151</t>
-  </si>
-  <si>
-    <t>0.9615,0.0445,0.0027,0.0021</t>
-  </si>
-  <si>
-    <t>0.8937,0.1008,0.0252,0.0047</t>
-  </si>
-  <si>
-    <t>0.0058,0.0110,0.9885,0.0038</t>
-  </si>
-  <si>
-    <t>0.9571,0.0362,0.0049,0.0060</t>
-  </si>
-  <si>
-    <t>0.0067,0.0495,0.9824,0.0012</t>
-  </si>
-  <si>
-    <t>0.0164,0.3771,0.8910,0.0095</t>
-  </si>
-  <si>
-    <t>0.0789,0.0101,0.9396,0.0024</t>
-  </si>
-  <si>
-    <t>0.0044,0.0418,0.9864,0.0010</t>
-  </si>
-  <si>
-    <t>0.0382,0.0063,0.9660,0.0034</t>
-  </si>
-  <si>
-    <t>0.0089,0.0008,0.9889,0.0028</t>
-  </si>
-  <si>
-    <t>0.0079,0.0322,0.9782,0.0061</t>
-  </si>
-  <si>
-    <t>0.6664,0.0261,0.3740,0.0070</t>
-  </si>
-  <si>
-    <t>0.3038,0.0208,0.7370,0.0149</t>
-  </si>
-  <si>
-    <t>0.7423,0.0437,0.2523,0.0076</t>
-  </si>
-  <si>
-    <t>0.4365,0.3200,0.3204,0.0717</t>
-  </si>
-  <si>
-    <t>0.1225,0.5885,0.4299,0.0070</t>
-  </si>
-  <si>
-    <t>0.6430,0.0319,0.3725,0.0116</t>
-  </si>
-  <si>
-    <t>0.4851,0.1755,0.4052,0.0701</t>
-  </si>
-  <si>
-    <t>0.5417,0.0255,0.5438,0.0047</t>
-  </si>
-  <si>
-    <t>0.3136,0.8048,0.0049,0.0003</t>
-  </si>
-  <si>
-    <t>0.6905,0.4965,0.0046,0.0005</t>
-  </si>
-  <si>
-    <t>0.5937,0.5598,0.0065,0.0013</t>
-  </si>
-  <si>
-    <t>0.9855,0.0114,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.7767,0.3395,0.0080,0.0009</t>
-  </si>
-  <si>
-    <t>0.3718,0.3721,0.3232,0.0093</t>
-  </si>
-  <si>
-    <t>0.7416,0.0290,0.2181,0.0234</t>
-  </si>
-  <si>
-    <t>0.6042,0.0361,0.2749,0.1173</t>
-  </si>
-  <si>
-    <t>0.6521,0.0105,0.3990,0.0112</t>
-  </si>
-  <si>
-    <t>0.8209,0.0223,0.1732,0.0085</t>
-  </si>
-  <si>
-    <t>0.0269,0.0093,0.9491,0.0294</t>
-  </si>
-  <si>
-    <t>0.0711,0.1000,0.8714,0.0185</t>
-  </si>
-  <si>
-    <t>0.0274,0.1823,0.9248,0.0063</t>
-  </si>
-  <si>
-    <t>0.0951,0.0514,0.8823,0.0179</t>
-  </si>
-  <si>
-    <t>0.0011,0.2058,0.9773,0.0003</t>
-  </si>
-  <si>
-    <t>0.9847,0.0021,0.0001,0.0050</t>
-  </si>
-  <si>
-    <t>0.9911,0.0045,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9604,0.0411,0.0061,0.0039</t>
-  </si>
-  <si>
-    <t>0.9759,0.0487,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9769,0.0279,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.9857,0.0125,0.0013,0.0018</t>
-  </si>
-  <si>
-    <t>0.9903,0.0031,0.0005,0.0031</t>
-  </si>
-  <si>
-    <t>0.9801,0.0095,0.0019,0.0039</t>
-  </si>
-  <si>
-    <t>0.2651,0.0344,0.7469,0.0230</t>
-  </si>
-  <si>
-    <t>0.3576,0.5734,0.1364,0.0076</t>
-  </si>
-  <si>
-    <t>0.3710,0.0197,0.0016,0.7502</t>
-  </si>
-  <si>
-    <t>0.0122,0.0106,0.9860,0.0007</t>
-  </si>
-  <si>
-    <t>0.0020,0.0257,0.9929,0.0008</t>
-  </si>
-  <si>
-    <t>0.0400,0.0092,0.9672,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0031,0.9976,0.0021</t>
-  </si>
-  <si>
-    <t>0.0454,0.0037,0.9664,0.0011</t>
-  </si>
-  <si>
-    <t>0.0012,0.0036,0.9962,0.0009</t>
-  </si>
-  <si>
-    <t>0.0108,0.0203,0.9725,0.0053</t>
-  </si>
-  <si>
-    <t>0.1980,0.2276,0.6262,0.0471</t>
-  </si>
-  <si>
-    <t>0.7078,0.0173,0.3302,0.0047</t>
-  </si>
-  <si>
-    <t>0.7199,0.0049,0.3172,0.0158</t>
-  </si>
-  <si>
-    <t>0.7048,0.0187,0.3055,0.0232</t>
-  </si>
-  <si>
-    <t>0.9889,0.0112,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9899,0.0050,0.0008,0.0014</t>
-  </si>
-  <si>
-    <t>0.9879,0.0079,0.0022,0.0007</t>
-  </si>
-  <si>
-    <t>0.9893,0.0127,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9815,0.0012,0.0001,0.0131</t>
-  </si>
-  <si>
-    <t>0.9870,0.0070,0.0010,0.0025</t>
-  </si>
-  <si>
-    <t>0.9880,0.0073,0.0010,0.0015</t>
-  </si>
-  <si>
-    <t>0.9815,0.0043,0.0003,0.0041</t>
-  </si>
-  <si>
-    <t>0.0297,0.0237,0.9513,0.0074</t>
-  </si>
-  <si>
-    <t>0.0057,0.0082,0.9797,0.0088</t>
-  </si>
-  <si>
-    <t>0.0110,0.0907,0.9471,0.0101</t>
-  </si>
-  <si>
-    <t>0.1997,0.0083,0.8357,0.0160</t>
-  </si>
-  <si>
-    <t>0.0042,0.0038,0.9844,0.0111</t>
-  </si>
-  <si>
-    <t>0.6185,0.0346,0.2962,0.0933</t>
-  </si>
-  <si>
-    <t>0.1743,0.1076,0.7190,0.0282</t>
-  </si>
-  <si>
-    <t>0.0592,0.0384,0.9196,0.0114</t>
-  </si>
-  <si>
-    <t>0.8505,0.0058,0.0088,0.1471</t>
-  </si>
-  <si>
-    <t>0.0046,0.0965,0.0042,0.9932</t>
-  </si>
-  <si>
-    <t>0.0142,0.0250,0.0013,0.9916</t>
-  </si>
-  <si>
-    <t>0.0034,0.0005,0.0024,0.9954</t>
-  </si>
-  <si>
-    <t>0.0049,0.0002,0.0006,0.9972</t>
-  </si>
-  <si>
-    <t>0.6780,0.0447,0.0588,0.2807</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.7676,0.0150,0.1311,0.0660</t>
+  </si>
+  <si>
+    <t>0.0380,0.0054,0.0020,0.9852</t>
+  </si>
+  <si>
+    <t>0.8788,0.0624,0.0489,0.0209</t>
+  </si>
+  <si>
+    <t>0.0199,0.0035,0.0009,0.9923</t>
+  </si>
+  <si>
+    <t>0.9945,0.0024,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9908,0.0027,0.0003,0.0020</t>
+  </si>
+  <si>
+    <t>0.9839,0.0066,0.0008,0.0046</t>
+  </si>
+  <si>
+    <t>0.9950,0.0022,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9851,0.0171,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9928,0.0051,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9945,0.0024,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9939,0.0033,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.7198,0.0296,0.2796,0.0158</t>
+  </si>
+  <si>
+    <t>0.4793,0.0054,0.6706,0.0045</t>
+  </si>
+  <si>
+    <t>0.7248,0.0086,0.3979,0.0004</t>
+  </si>
+  <si>
+    <t>0.3983,0.0225,0.6600,0.0063</t>
+  </si>
+  <si>
+    <t>0.4340,0.0528,0.6100,0.0170</t>
+  </si>
+  <si>
+    <t>0.0189,0.9693,0.0047,0.0022</t>
+  </si>
+  <si>
+    <t>0.0130,0.9833,0.0036,0.0004</t>
+  </si>
+  <si>
+    <t>0.5648,0.5938,0.0066,0.0004</t>
+  </si>
+  <si>
+    <t>0.0284,0.9593,0.0025,0.0030</t>
+  </si>
+  <si>
+    <t>0.0396,0.9658,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.4699,0.0130,0.5800,0.0270</t>
+  </si>
+  <si>
+    <t>0.4096,0.0234,0.5338,0.0792</t>
+  </si>
+  <si>
+    <t>0.1056,0.0239,0.8730,0.0035</t>
+  </si>
+  <si>
+    <t>0.3836,0.0096,0.6759,0.0222</t>
+  </si>
+  <si>
+    <t>0.0297,0.0034,0.9778,0.0009</t>
+  </si>
+  <si>
+    <t>0.0044,0.0018,0.9882,0.0048</t>
+  </si>
+  <si>
+    <t>0.0607,0.0035,0.9492,0.0074</t>
+  </si>
+  <si>
+    <t>0.4394,0.6636,0.0075,0.0023</t>
+  </si>
+  <si>
+    <t>0.4910,0.4208,0.1593,0.1257</t>
+  </si>
+  <si>
+    <t>0.0090,0.0227,0.9730,0.0172</t>
+  </si>
+  <si>
+    <t>0.0261,0.4446,0.7542,0.0018</t>
+  </si>
+  <si>
+    <t>0.6720,0.2708,0.0623,0.0868</t>
+  </si>
+  <si>
+    <t>0.8525,0.1032,0.0478,0.0127</t>
+  </si>
+  <si>
+    <t>0.7711,0.3095,0.0135,0.0005</t>
+  </si>
+  <si>
+    <t>0.3647,0.6511,0.1382,0.0065</t>
+  </si>
+  <si>
+    <t>0.0830,0.5126,0.6228,0.0229</t>
+  </si>
+  <si>
+    <t>0.0258,0.0399,0.9340,0.0247</t>
+  </si>
+  <si>
+    <t>0.1750,0.1948,0.6646,0.0671</t>
+  </si>
+  <si>
+    <t>0.3836,0.0261,0.6514,0.0140</t>
+  </si>
+  <si>
+    <t>0.0249,0.1839,0.9318,0.0022</t>
+  </si>
+  <si>
+    <t>0.0053,0.9744,0.1129,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.0068,0.9869,0.0117</t>
+  </si>
+  <si>
+    <t>0.1010,0.5069,0.0349,0.8621</t>
+  </si>
+  <si>
+    <t>0.0545,0.8896,0.1111,0.0304</t>
+  </si>
+  <si>
+    <t>0.0021,0.9805,0.2414,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.9936,0.1036,0.0012</t>
+  </si>
+  <si>
+    <t>0.0037,0.3436,0.9759,0.0014</t>
+  </si>
+  <si>
+    <t>0.0014,0.6038,0.9613,0.0006</t>
+  </si>
+  <si>
+    <t>0.1230,0.0429,0.8596,0.0153</t>
+  </si>
+  <si>
+    <t>0.0297,0.0019,0.9721,0.0046</t>
+  </si>
+  <si>
+    <t>0.0034,0.0048,0.9848,0.0117</t>
+  </si>
+  <si>
+    <t>0.0053,0.1017,0.9786,0.0016</t>
+  </si>
+  <si>
+    <t>0.9678,0.0357,0.0040,0.0010</t>
+  </si>
+  <si>
+    <t>0.9764,0.0063,0.0095,0.0036</t>
+  </si>
+  <si>
+    <t>0.9501,0.0460,0.0031,0.0066</t>
+  </si>
+  <si>
+    <t>0.0030,0.0266,0.9894,0.0045</t>
+  </si>
+  <si>
+    <t>0.9835,0.0121,0.0032,0.0008</t>
+  </si>
+  <si>
+    <t>0.9904,0.0081,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9703,0.0253,0.0054,0.0027</t>
+  </si>
+  <si>
+    <t>0.0011,0.9305,0.8511,0.0001</t>
+  </si>
+  <si>
+    <t>0.0052,0.2305,0.9678,0.0009</t>
+  </si>
+  <si>
+    <t>0.0050,0.0138,0.9859,0.0037</t>
+  </si>
+  <si>
+    <t>0.0030,0.7085,0.9382,0.0011</t>
+  </si>
+  <si>
+    <t>0.0009,0.0023,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.0311,0.9225,0.0432,0.0006</t>
+  </si>
+  <si>
+    <t>0.0235,0.9724,0.0069,0.0001</t>
+  </si>
+  <si>
+    <t>0.6690,0.1529,0.2517,0.0121</t>
+  </si>
+  <si>
+    <t>0.7036,0.1067,0.2119,0.0184</t>
+  </si>
+  <si>
+    <t>0.0371,0.1361,0.9261,0.0226</t>
+  </si>
+  <si>
+    <t>0.0060,0.5912,0.8854,0.0004</t>
+  </si>
+  <si>
+    <t>0.0013,0.9090,0.8343,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9932,0.0791,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9321,0.8815,0.0012</t>
+  </si>
+  <si>
+    <t>0.0419,0.0128,0.0968,0.9209</t>
+  </si>
+  <si>
+    <t>0.0013,0.0020,0.0002,0.9991</t>
+  </si>
+  <si>
+    <t>0.0080,0.0427,0.0037,0.9929</t>
+  </si>
+  <si>
+    <t>0.0062,0.0076,0.0025,0.9951</t>
+  </si>
+  <si>
+    <t>0.0149,0.0103,0.0255,0.9779</t>
+  </si>
+  <si>
+    <t>0.0041,0.0140,0.0008,0.9973</t>
+  </si>
+  <si>
+    <t>0.0019,0.9129,0.7950,0.0015</t>
+  </si>
+  <si>
+    <t>0.0017,0.7177,0.9504,0.0004</t>
+  </si>
+  <si>
+    <t>0.0107,0.4425,0.9006,0.0021</t>
+  </si>
+  <si>
+    <t>0.0031,0.6209,0.9353,0.0015</t>
+  </si>
+  <si>
+    <t>0.0032,0.8635,0.7302,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9135,0.8901,0.0001</t>
+  </si>
+  <si>
+    <t>0.9949,0.0029,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9630,0.0428,0.0059,0.0017</t>
+  </si>
+  <si>
+    <t>0.9618,0.0506,0.0033,0.0015</t>
+  </si>
+  <si>
+    <t>0.9896,0.0087,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9883,0.0043,0.0005,0.0022</t>
+  </si>
+  <si>
+    <t>0.9963,0.0019,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9690,0.0197,0.0011,0.0041</t>
+  </si>
+  <si>
+    <t>0.9849,0.0158,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9927,0.0026,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9921,0.0067,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9939,0.0003,0.0000,0.0028</t>
+  </si>
+  <si>
+    <t>0.9964,0.0017,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9871,0.0071,0.0008,0.0016</t>
+  </si>
+  <si>
+    <t>0.9947,0.0008,0.0002,0.0018</t>
+  </si>
+  <si>
+    <t>0.9850,0.0025,0.0002,0.0049</t>
+  </si>
+  <si>
+    <t>0.9876,0.0065,0.0026,0.0015</t>
+  </si>
+  <si>
+    <t>0.0003,0.0008,0.9930,0.0123</t>
+  </si>
+  <si>
+    <t>0.0766,0.0249,0.9164,0.0050</t>
+  </si>
+  <si>
+    <t>0.5087,0.0098,0.5590,0.0132</t>
+  </si>
+  <si>
+    <t>0.0677,0.0126,0.9249,0.0052</t>
+  </si>
+  <si>
+    <t>0.0197,0.9773,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0480,0.9460,0.0122,0.0002</t>
+  </si>
+  <si>
+    <t>0.1146,0.9185,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.1441,0.8153,0.0091,0.0403</t>
+  </si>
+  <si>
+    <t>0.0234,0.9693,0.0124,0.0005</t>
+  </si>
+  <si>
+    <t>0.0165,0.9783,0.0039,0.0002</t>
+  </si>
+  <si>
+    <t>0.8273,0.2496,0.0108,0.0010</t>
+  </si>
+  <si>
+    <t>0.5784,0.1931,0.3120,0.0197</t>
+  </si>
+  <si>
+    <t>0.4992,0.0237,0.5607,0.0069</t>
+  </si>
+  <si>
+    <t>0.7560,0.0199,0.2304,0.0093</t>
+  </si>
+  <si>
+    <t>0.4944,0.0125,0.5778,0.0200</t>
+  </si>
+  <si>
+    <t>0.0512,0.2086,0.0204,0.9548</t>
+  </si>
+  <si>
+    <t>0.0034,0.9866,0.0377,0.0015</t>
+  </si>
+  <si>
+    <t>0.0023,0.9851,0.0520,0.0029</t>
+  </si>
+  <si>
+    <t>0.0432,0.9125,0.0157,0.0725</t>
+  </si>
+  <si>
+    <t>0.0002,0.9368,0.9468,0.0002</t>
+  </si>
+  <si>
+    <t>0.0200,0.9722,0.0336,0.0002</t>
+  </si>
+  <si>
+    <t>0.6004,0.5127,0.0170,0.0015</t>
+  </si>
+  <si>
+    <t>0.5439,0.4766,0.0457,0.0021</t>
+  </si>
+  <si>
+    <t>0.9661,0.0155,0.0065,0.0050</t>
+  </si>
+  <si>
+    <t>0.9830,0.0043,0.0020,0.0058</t>
+  </si>
+  <si>
+    <t>0.9829,0.0045,0.0017,0.0068</t>
+  </si>
+  <si>
+    <t>0.9573,0.0099,0.0059,0.0143</t>
+  </si>
+  <si>
+    <t>0.9914,0.0089,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9561,0.0224,0.0054,0.0073</t>
+  </si>
+  <si>
+    <t>0.9857,0.0025,0.0016,0.0052</t>
+  </si>
+  <si>
+    <t>0.9731,0.0101,0.0051,0.0086</t>
+  </si>
+  <si>
+    <t>0.0290,0.4961,0.7990,0.0063</t>
+  </si>
+  <si>
+    <t>0.0030,0.4557,0.9610,0.0005</t>
+  </si>
+  <si>
+    <t>0.0223,0.2639,0.8414,0.0005</t>
+  </si>
+  <si>
+    <t>0.0186,0.2509,0.8286,0.0004</t>
+  </si>
+  <si>
+    <t>0.4630,0.0199,0.5815,0.0163</t>
+  </si>
+  <si>
+    <t>0.8248,0.0818,0.0897,0.0139</t>
+  </si>
+  <si>
+    <t>0.4437,0.0085,0.6200,0.0331</t>
+  </si>
+  <si>
+    <t>0.6435,0.1618,0.2707,0.0308</t>
+  </si>
+  <si>
+    <t>0.0885,0.0196,0.0348,0.9278</t>
+  </si>
+  <si>
+    <t>0.0007,0.0011,0.0039,0.9977</t>
+  </si>
+  <si>
+    <t>0.0029,0.0096,0.0025,0.9964</t>
+  </si>
+  <si>
+    <t>0.0091,0.0010,0.0027,0.9931</t>
+  </si>
+  <si>
+    <t>0.0039,0.9511,0.4087,0.0004</t>
+  </si>
+  <si>
+    <t>0.9830,0.0139,0.0014,0.0022</t>
+  </si>
+  <si>
+    <t>0.5821,0.5061,0.0182,0.0050</t>
+  </si>
+  <si>
+    <t>0.9560,0.0426,0.0071,0.0031</t>
+  </si>
+  <si>
+    <t>0.5983,0.5035,0.0098,0.0001</t>
+  </si>
+  <si>
+    <t>0.9228,0.0100,0.0066,0.0617</t>
+  </si>
+  <si>
+    <t>0.1734,0.0310,0.0127,0.9151</t>
+  </si>
+  <si>
+    <t>0.9805,0.0050,0.0011,0.0055</t>
+  </si>
+  <si>
+    <t>0.0019,0.0723,0.9709,0.0372</t>
+  </si>
+  <si>
+    <t>0.3934,0.0007,0.0105,0.6492</t>
+  </si>
+  <si>
+    <t>0.8948,0.0121,0.0171,0.0520</t>
+  </si>
+  <si>
+    <t>0.5652,0.4889,0.0275,0.0055</t>
+  </si>
+  <si>
+    <t>0.9051,0.0331,0.0354,0.0145</t>
+  </si>
+  <si>
+    <t>0.8682,0.0817,0.0503,0.0021</t>
+  </si>
+  <si>
+    <t>0.5309,0.1595,0.3917,0.0215</t>
+  </si>
+  <si>
+    <t>0.7678,0.1569,0.1092,0.0124</t>
+  </si>
+  <si>
+    <t>0.8756,0.0657,0.0363,0.0115</t>
+  </si>
+  <si>
+    <t>0.9928,0.0032,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.9880,0.0088,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9720,0.0098,0.0022,0.0095</t>
+  </si>
+  <si>
+    <t>0.9886,0.0030,0.0011,0.0025</t>
+  </si>
+  <si>
+    <t>0.9666,0.0220,0.0070,0.0064</t>
+  </si>
+  <si>
+    <t>0.9794,0.0066,0.0009,0.0074</t>
+  </si>
+  <si>
+    <t>0.9912,0.0017,0.0004,0.0030</t>
+  </si>
+  <si>
+    <t>0.9900,0.0035,0.0007,0.0026</t>
+  </si>
+  <si>
+    <t>0.6456,0.4497,0.0060,0.0065</t>
+  </si>
+  <si>
+    <t>0.7488,0.4182,0.0045,0.0002</t>
+  </si>
+  <si>
+    <t>0.7623,0.3361,0.0105,0.0006</t>
+  </si>
+  <si>
+    <t>0.7193,0.2373,0.1135,0.0354</t>
+  </si>
+  <si>
+    <t>0.9713,0.0364,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.8588,0.1488,0.0205,0.0086</t>
+  </si>
+  <si>
+    <t>0.9178,0.1008,0.0135,0.0008</t>
+  </si>
+  <si>
+    <t>0.9233,0.0833,0.0115,0.0017</t>
+  </si>
+  <si>
+    <t>0.0010,0.0541,0.9933,0.0007</t>
+  </si>
+  <si>
+    <t>0.8994,0.1446,0.0083,0.0013</t>
+  </si>
+  <si>
+    <t>0.0007,0.0020,0.9953,0.0035</t>
+  </si>
+  <si>
+    <t>0.0038,0.4871,0.9515,0.0027</t>
+  </si>
+  <si>
+    <t>0.2833,0.0105,0.8014,0.0025</t>
+  </si>
+  <si>
+    <t>0.0115,0.0449,0.9741,0.0045</t>
+  </si>
+  <si>
+    <t>0.0730,0.0100,0.9440,0.0020</t>
+  </si>
+  <si>
+    <t>0.0086,0.0011,0.9914,0.0011</t>
+  </si>
+  <si>
+    <t>0.0156,0.0142,0.9796,0.0018</t>
+  </si>
+  <si>
+    <t>0.5991,0.0347,0.4359,0.0039</t>
+  </si>
+  <si>
+    <t>0.1508,0.0072,0.8969,0.0015</t>
+  </si>
+  <si>
+    <t>0.1385,0.2430,0.5562,0.0029</t>
+  </si>
+  <si>
+    <t>0.2956,0.0848,0.6599,0.0061</t>
+  </si>
+  <si>
+    <t>0.2546,0.5028,0.3262,0.0208</t>
+  </si>
+  <si>
+    <t>0.7285,0.0733,0.2279,0.0057</t>
+  </si>
+  <si>
+    <t>0.3036,0.3119,0.3777,0.0182</t>
+  </si>
+  <si>
+    <t>0.7516,0.0225,0.2706,0.0048</t>
+  </si>
+  <si>
+    <t>0.8267,0.3285,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.1915,0.8845,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.8919,0.2116,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.9692,0.0404,0.0023,0.0005</t>
+  </si>
+  <si>
+    <t>0.8997,0.1497,0.0066,0.0021</t>
+  </si>
+  <si>
+    <t>0.5884,0.1971,0.2652,0.0249</t>
+  </si>
+  <si>
+    <t>0.8742,0.0037,0.1454,0.0055</t>
+  </si>
+  <si>
+    <t>0.5371,0.0183,0.4751,0.0367</t>
+  </si>
+  <si>
+    <t>0.6766,0.0094,0.3002,0.0300</t>
+  </si>
+  <si>
+    <t>0.5137,0.0608,0.4895,0.0529</t>
+  </si>
+  <si>
+    <t>0.0017,0.0189,0.9672,0.0487</t>
+  </si>
+  <si>
+    <t>0.0661,0.2157,0.8004,0.0354</t>
+  </si>
+  <si>
+    <t>0.0090,0.1043,0.9548,0.0192</t>
+  </si>
+  <si>
+    <t>0.2126,0.1037,0.6920,0.0626</t>
+  </si>
+  <si>
+    <t>0.0055,0.5139,0.9044,0.0026</t>
+  </si>
+  <si>
+    <t>0.9807,0.0049,0.0003,0.0041</t>
+  </si>
+  <si>
+    <t>0.9807,0.0159,0.0008,0.0019</t>
+  </si>
+  <si>
+    <t>0.9793,0.0284,0.0023,0.0005</t>
+  </si>
+  <si>
+    <t>0.9927,0.0058,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9699,0.0294,0.0028,0.0020</t>
+  </si>
+  <si>
+    <t>0.9899,0.0073,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9938,0.0020,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9867,0.0028,0.0004,0.0036</t>
+  </si>
+  <si>
+    <t>0.1030,0.0066,0.9238,0.0073</t>
+  </si>
+  <si>
+    <t>0.3669,0.1272,0.5916,0.0173</t>
+  </si>
+  <si>
+    <t>0.8843,0.0378,0.0755,0.0039</t>
+  </si>
+  <si>
+    <t>0.0033,0.0212,0.9910,0.0011</t>
+  </si>
+  <si>
+    <t>0.0120,0.0333,0.9604,0.0211</t>
+  </si>
+  <si>
+    <t>0.0260,0.1252,0.9359,0.0011</t>
+  </si>
+  <si>
+    <t>0.0008,0.0022,0.9942,0.0042</t>
+  </si>
+  <si>
+    <t>0.0599,0.0168,0.9446,0.0021</t>
+  </si>
+  <si>
+    <t>0.0011,0.0087,0.9968,0.0004</t>
+  </si>
+  <si>
+    <t>0.0166,0.0086,0.9766,0.0038</t>
+  </si>
+  <si>
+    <t>0.1986,0.0853,0.7485,0.0099</t>
+  </si>
+  <si>
+    <t>0.5794,0.0159,0.4899,0.0086</t>
+  </si>
+  <si>
+    <t>0.6113,0.0502,0.3732,0.0292</t>
+  </si>
+  <si>
+    <t>0.7670,0.0113,0.2623,0.0073</t>
+  </si>
+  <si>
+    <t>0.9848,0.0016,0.0001,0.0053</t>
+  </si>
+  <si>
+    <t>0.9965,0.0038,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9839,0.0084,0.0008,0.0021</t>
+  </si>
+  <si>
+    <t>0.9857,0.0106,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.9879,0.0023,0.0002,0.0034</t>
+  </si>
+  <si>
+    <t>0.9939,0.0062,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9626,0.0577,0.0039,0.0006</t>
+  </si>
+  <si>
+    <t>0.9458,0.0728,0.0036,0.0014</t>
+  </si>
+  <si>
+    <t>0.0451,0.0415,0.9213,0.0009</t>
+  </si>
+  <si>
+    <t>0.0131,0.0417,0.9710,0.0048</t>
+  </si>
+  <si>
+    <t>0.0058,0.0728,0.9752,0.0062</t>
+  </si>
+  <si>
+    <t>0.0986,0.0084,0.9226,0.0008</t>
+  </si>
+  <si>
+    <t>0.0010,0.0054,0.9889,0.0130</t>
+  </si>
+  <si>
+    <t>0.2841,0.0309,0.4619,0.2682</t>
+  </si>
+  <si>
+    <t>0.1105,0.0316,0.8534,0.0499</t>
+  </si>
+  <si>
+    <t>0.0958,0.1893,0.8325,0.0324</t>
+  </si>
+  <si>
+    <t>0.8674,0.0028,0.0272,0.0563</t>
+  </si>
+  <si>
+    <t>0.0631,0.0169,0.0133,0.9634</t>
+  </si>
+  <si>
+    <t>0.0069,0.0264,0.0014,0.9948</t>
+  </si>
+  <si>
+    <t>0.0102,0.0007,0.0006,0.9950</t>
+  </si>
+  <si>
+    <t>0.0047,0.0004,0.0001,0.9984</t>
+  </si>
+  <si>
+    <t>0.2035,0.0125,0.0140,0.8825</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2525,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2651,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3606,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3858,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3900,7 @@
         <v>261</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4600,7 @@
         <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4656,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,10 +5059,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
